--- a/artfynd/S 4708-2022 artfynd.xlsx
+++ b/artfynd/S 4708-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Andersson, M. Utredningsobj. H-län 2007</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/327314</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Andersson, M. Utredningsobj. H-län 2007</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/727568</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
           <t>Andersson, M. Utredningsobj. H-län 2007</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/727569</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236209</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236224</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236225</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236226</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236186</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236187</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236192</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
           <t>Andersson, M. Utredningsobj. H-län 2007</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1188656</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
           <t>Andersson, M. Utredningsobj. H-län 2007</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1188657</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,6 +2130,11 @@
           <t>Andersson, M. Utredningsobj. H-län 2007</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1865371</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2167,6 +2237,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134235919</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2269,6 +2344,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134235918</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2371,6 +2451,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236061</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2473,6 +2558,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236479</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2575,6 +2665,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236483</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2672,6 +2767,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236122</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2774,6 +2874,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236140</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2876,6 +2981,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236141</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2978,6 +3088,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236143</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3080,6 +3195,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236144</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3182,6 +3302,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236169</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3288,6 +3413,11 @@
           <t>Andersson, M. Utredningsobj. H-län 2007</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3784647</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3390,6 +3520,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3487,6 +3622,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236326</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3584,6 +3724,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236327</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3681,6 +3826,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236328</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3783,6 +3933,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236347</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3885,6 +4040,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236371</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3987,6 +4147,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236372</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4089,6 +4254,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236373</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4191,6 +4361,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236374</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4293,6 +4468,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236375</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4390,6 +4570,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236389</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4492,8 +4677,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236390</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>